--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/08-report/CYC-1-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/08-report/CYC-1-cycle-report.xlsx
@@ -170,7 +170,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-05T16:03:52.180Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-05T16:26:38.592Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -4990,7 +4990,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-05T16:03:53.130Z</t>
+    <t>2026-10-05T16:26:39.468Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -23937,7 +23937,7 @@
         <v>1298</v>
       </c>
       <c r="E2" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -24055,7 +24055,7 @@
         <v>1298</v>
       </c>
       <c r="E8" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -24073,7 +24073,7 @@
         <v>1298</v>
       </c>
       <c r="E9" s="2">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -24091,7 +24091,7 @@
         <v>1298</v>
       </c>
       <c r="E10" s="2">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -24109,7 +24109,7 @@
         <v>1298</v>
       </c>
       <c r="E11" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -24127,7 +24127,7 @@
         <v>1298</v>
       </c>
       <c r="E12" s="2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -24145,7 +24145,7 @@
         <v>1298</v>
       </c>
       <c r="E13" s="2">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -24223,7 +24223,7 @@
         <v>1298</v>
       </c>
       <c r="E17" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -24241,7 +24241,7 @@
         <v>1298</v>
       </c>
       <c r="E18" s="2">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -24299,7 +24299,7 @@
         <v>1298</v>
       </c>
       <c r="E21" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -24337,7 +24337,7 @@
         <v>1298</v>
       </c>
       <c r="E23" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -24355,7 +24355,7 @@
         <v>1298</v>
       </c>
       <c r="E24" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -24373,7 +24373,7 @@
         <v>1298</v>
       </c>
       <c r="E25" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -24391,7 +24391,7 @@
         <v>1298</v>
       </c>
       <c r="E26" s="2">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -24409,7 +24409,7 @@
         <v>1298</v>
       </c>
       <c r="E27" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -24427,7 +24427,7 @@
         <v>1298</v>
       </c>
       <c r="E28" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -24445,7 +24445,7 @@
         <v>1298</v>
       </c>
       <c r="E29" s="2">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -24463,7 +24463,7 @@
         <v>1298</v>
       </c>
       <c r="E30" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -24481,7 +24481,7 @@
         <v>1298</v>
       </c>
       <c r="E31" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -24519,7 +24519,7 @@
         <v>1298</v>
       </c>
       <c r="E33" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -24537,7 +24537,7 @@
         <v>1298</v>
       </c>
       <c r="E34" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -24595,7 +24595,7 @@
         <v>1298</v>
       </c>
       <c r="E37" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -24633,7 +24633,7 @@
         <v>1298</v>
       </c>
       <c r="E39" s="2">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -24651,7 +24651,7 @@
         <v>1298</v>
       </c>
       <c r="E40" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -24749,7 +24749,7 @@
         <v>1298</v>
       </c>
       <c r="E45" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -24767,7 +24767,7 @@
         <v>1298</v>
       </c>
       <c r="E46" s="2">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -24785,7 +24785,7 @@
         <v>1298</v>
       </c>
       <c r="E47" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -24823,7 +24823,7 @@
         <v>1298</v>
       </c>
       <c r="E49" s="2">
-        <v>265</v>
+        <v>222</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -24859,7 +24859,7 @@
         <v>1298</v>
       </c>
       <c r="E51" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -24977,7 +24977,7 @@
         <v>1298</v>
       </c>
       <c r="E57" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -24995,7 +24995,7 @@
         <v>1298</v>
       </c>
       <c r="E58" s="2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -25033,7 +25033,7 @@
         <v>1298</v>
       </c>
       <c r="E60" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -25149,7 +25149,7 @@
         <v>1298</v>
       </c>
       <c r="E66" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -25167,7 +25167,7 @@
         <v>1298</v>
       </c>
       <c r="E67" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -25225,7 +25225,7 @@
         <v>1298</v>
       </c>
       <c r="E70" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -25243,7 +25243,7 @@
         <v>1298</v>
       </c>
       <c r="E71" s="2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -25261,7 +25261,7 @@
         <v>1298</v>
       </c>
       <c r="E72" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -25299,7 +25299,7 @@
         <v>1298</v>
       </c>
       <c r="E74" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -25317,7 +25317,7 @@
         <v>1298</v>
       </c>
       <c r="E75" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -25335,7 +25335,7 @@
         <v>1298</v>
       </c>
       <c r="E76" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -25411,7 +25411,7 @@
         <v>1298</v>
       </c>
       <c r="E80" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -25429,7 +25429,7 @@
         <v>1298</v>
       </c>
       <c r="E81" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -25447,7 +25447,7 @@
         <v>1298</v>
       </c>
       <c r="E82" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -25525,7 +25525,7 @@
         <v>1298</v>
       </c>
       <c r="E86" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -25543,7 +25543,7 @@
         <v>1298</v>
       </c>
       <c r="E87" s="2">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -25561,7 +25561,7 @@
         <v>1298</v>
       </c>
       <c r="E88" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -25579,7 +25579,7 @@
         <v>1298</v>
       </c>
       <c r="E89" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -25635,7 +25635,7 @@
         <v>1298</v>
       </c>
       <c r="E92" s="2">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -25673,7 +25673,7 @@
         <v>1298</v>
       </c>
       <c r="E94" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -25751,7 +25751,7 @@
         <v>1298</v>
       </c>
       <c r="E98" s="2">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -25869,7 +25869,7 @@
         <v>1298</v>
       </c>
       <c r="E104" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -25907,7 +25907,7 @@
         <v>1298</v>
       </c>
       <c r="E106" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -26045,7 +26045,7 @@
         <v>1298</v>
       </c>
       <c r="E113" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -26123,7 +26123,7 @@
         <v>1298</v>
       </c>
       <c r="E117" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -26159,7 +26159,7 @@
         <v>1301</v>
       </c>
       <c r="E119" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -26177,7 +26177,7 @@
         <v>1298</v>
       </c>
       <c r="E120" s="2">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -26195,7 +26195,7 @@
         <v>1298</v>
       </c>
       <c r="E121" s="2">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -26213,7 +26213,7 @@
         <v>1301</v>
       </c>
       <c r="E122" s="2">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -26231,7 +26231,7 @@
         <v>1298</v>
       </c>
       <c r="E123" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -26249,7 +26249,7 @@
         <v>1298</v>
       </c>
       <c r="E124" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -26267,7 +26267,7 @@
         <v>1298</v>
       </c>
       <c r="E125" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -26285,7 +26285,7 @@
         <v>1298</v>
       </c>
       <c r="E126" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -26303,7 +26303,7 @@
         <v>1298</v>
       </c>
       <c r="E127" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -26339,7 +26339,7 @@
         <v>1298</v>
       </c>
       <c r="E129" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -26393,7 +26393,7 @@
         <v>1298</v>
       </c>
       <c r="E132" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -26411,7 +26411,7 @@
         <v>1298</v>
       </c>
       <c r="E133" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F133" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/08-report/CYC-1-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/08-report/CYC-1-cycle-report.xlsx
@@ -116,7 +116,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking baseline · Functional (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 132 test cases are designed, 74 of them automated in 58 Playwright scripts. Execution ran 74 automated cases for real: 71 passed and 3 failed (pass rate 95.9%). 3 defect(s) were raised from real failures: DEF-001 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-002 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-003 9 rooms in one search are rejected: returns 200 instead of 400.</t>
+    <t>Hotel booking baseline · Functional (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform (452df41) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 132 test cases are designed, 74 of them automated in 58 Playwright scripts. Execution ran 74 automated cases for real: 71 passed and 3 failed (pass rate 95.9%). 3 defect(s) were raised from real failures: DEF-001 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-002 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-003 9 rooms in one search are rejected: returns 200 instead of 400.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -149,7 +149,7 @@
     <t>jira-export</t>
   </si>
   <si>
-    <t>Jira export on GitHub (sri465inno/uc-agentic-quality-engineering@demo/jira-export): Jira REST API v3 JSON of AQPI-1, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
+    <t>Jira export on GitHub (sri465inno/EQE-MVP-Neeraj@demo/jira-export): Jira REST API v3 JSON of AQPI-1, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
   </si>
   <si>
     <t>Jira epic</t>
@@ -158,19 +158,19 @@
     <t>AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27</t>
   </si>
   <si>
-    <t>Jira export on GitHub (sri465inno/uc-agentic-quality-engineering@demo/jira-export): Jira REST API v3 JSON of AQPI-2, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
+    <t>Jira export on GitHub (sri465inno/EQE-MVP-Neeraj@demo/jira-export): Jira REST API v3 JSON of AQPI-2, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
   </si>
   <si>
     <t>Codebase</t>
   </si>
   <si>
-    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41)</t>
+    <t>sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform (452df41)</t>
   </si>
   <si>
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-05T16:26:38.592Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform (452df41) at 2026-10-05T16:57:11.522Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -4990,7 +4990,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-05T16:26:39.468Z</t>
+    <t>2026-10-05T16:57:14.953Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -23937,7 +23937,7 @@
         <v>1298</v>
       </c>
       <c r="E2" s="2">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -24055,7 +24055,7 @@
         <v>1298</v>
       </c>
       <c r="E8" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -24091,7 +24091,7 @@
         <v>1298</v>
       </c>
       <c r="E10" s="2">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -24109,7 +24109,7 @@
         <v>1298</v>
       </c>
       <c r="E11" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -24127,7 +24127,7 @@
         <v>1298</v>
       </c>
       <c r="E12" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -24145,7 +24145,7 @@
         <v>1298</v>
       </c>
       <c r="E13" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -24223,7 +24223,7 @@
         <v>1298</v>
       </c>
       <c r="E17" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -24241,7 +24241,7 @@
         <v>1298</v>
       </c>
       <c r="E18" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -24299,7 +24299,7 @@
         <v>1298</v>
       </c>
       <c r="E21" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -24337,7 +24337,7 @@
         <v>1298</v>
       </c>
       <c r="E23" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -24355,7 +24355,7 @@
         <v>1298</v>
       </c>
       <c r="E24" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -24373,7 +24373,7 @@
         <v>1298</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -24391,7 +24391,7 @@
         <v>1298</v>
       </c>
       <c r="E26" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -24409,7 +24409,7 @@
         <v>1298</v>
       </c>
       <c r="E27" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -24427,7 +24427,7 @@
         <v>1298</v>
       </c>
       <c r="E28" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -24445,7 +24445,7 @@
         <v>1298</v>
       </c>
       <c r="E29" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -24481,7 +24481,7 @@
         <v>1298</v>
       </c>
       <c r="E31" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -24519,7 +24519,7 @@
         <v>1298</v>
       </c>
       <c r="E33" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -24537,7 +24537,7 @@
         <v>1298</v>
       </c>
       <c r="E34" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -24595,7 +24595,7 @@
         <v>1298</v>
       </c>
       <c r="E37" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -24633,7 +24633,7 @@
         <v>1298</v>
       </c>
       <c r="E39" s="2">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -24651,7 +24651,7 @@
         <v>1298</v>
       </c>
       <c r="E40" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -24749,7 +24749,7 @@
         <v>1298</v>
       </c>
       <c r="E45" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -24785,7 +24785,7 @@
         <v>1298</v>
       </c>
       <c r="E47" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -24823,7 +24823,7 @@
         <v>1298</v>
       </c>
       <c r="E49" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -24841,7 +24841,7 @@
         <v>1298</v>
       </c>
       <c r="E50" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -24977,7 +24977,7 @@
         <v>1298</v>
       </c>
       <c r="E57" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -24995,7 +24995,7 @@
         <v>1298</v>
       </c>
       <c r="E58" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -25033,7 +25033,7 @@
         <v>1298</v>
       </c>
       <c r="E60" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -25131,7 +25131,7 @@
         <v>1298</v>
       </c>
       <c r="E65" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -25149,7 +25149,7 @@
         <v>1298</v>
       </c>
       <c r="E66" s="2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -25167,7 +25167,7 @@
         <v>1298</v>
       </c>
       <c r="E67" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -25225,7 +25225,7 @@
         <v>1298</v>
       </c>
       <c r="E70" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -25243,7 +25243,7 @@
         <v>1298</v>
       </c>
       <c r="E71" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -25261,7 +25261,7 @@
         <v>1298</v>
       </c>
       <c r="E72" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -25299,7 +25299,7 @@
         <v>1298</v>
       </c>
       <c r="E74" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -25335,7 +25335,7 @@
         <v>1298</v>
       </c>
       <c r="E76" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -25353,7 +25353,7 @@
         <v>1298</v>
       </c>
       <c r="E77" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -25429,7 +25429,7 @@
         <v>1298</v>
       </c>
       <c r="E81" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -25447,7 +25447,7 @@
         <v>1298</v>
       </c>
       <c r="E82" s="2">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -25525,7 +25525,7 @@
         <v>1298</v>
       </c>
       <c r="E86" s="2">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -25579,7 +25579,7 @@
         <v>1298</v>
       </c>
       <c r="E89" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -25597,7 +25597,7 @@
         <v>1298</v>
       </c>
       <c r="E90" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -25635,7 +25635,7 @@
         <v>1298</v>
       </c>
       <c r="E92" s="2">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -25673,7 +25673,7 @@
         <v>1298</v>
       </c>
       <c r="E94" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -25751,7 +25751,7 @@
         <v>1298</v>
       </c>
       <c r="E98" s="2">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -25869,7 +25869,7 @@
         <v>1298</v>
       </c>
       <c r="E104" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -25907,7 +25907,7 @@
         <v>1298</v>
       </c>
       <c r="E106" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -26045,7 +26045,7 @@
         <v>1298</v>
       </c>
       <c r="E113" s="2">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -26123,7 +26123,7 @@
         <v>1298</v>
       </c>
       <c r="E117" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -26159,7 +26159,7 @@
         <v>1301</v>
       </c>
       <c r="E119" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -26177,7 +26177,7 @@
         <v>1298</v>
       </c>
       <c r="E120" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -26195,7 +26195,7 @@
         <v>1298</v>
       </c>
       <c r="E121" s="2">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -26213,7 +26213,7 @@
         <v>1301</v>
       </c>
       <c r="E122" s="2">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -26231,7 +26231,7 @@
         <v>1298</v>
       </c>
       <c r="E123" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -26249,7 +26249,7 @@
         <v>1298</v>
       </c>
       <c r="E124" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -26267,7 +26267,7 @@
         <v>1298</v>
       </c>
       <c r="E125" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -26303,7 +26303,7 @@
         <v>1298</v>
       </c>
       <c r="E127" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -26321,7 +26321,7 @@
         <v>1298</v>
       </c>
       <c r="E128" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -26339,7 +26339,7 @@
         <v>1298</v>
       </c>
       <c r="E129" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -26357,7 +26357,7 @@
         <v>1298</v>
       </c>
       <c r="E130" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -26375,7 +26375,7 @@
         <v>1301</v>
       </c>
       <c r="E131" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -26393,7 +26393,7 @@
         <v>1298</v>
       </c>
       <c r="E132" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -26411,7 +26411,7 @@
         <v>1298</v>
       </c>
       <c r="E133" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F133" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/08-report/CYC-1-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/08-report/CYC-1-cycle-report.xlsx
@@ -170,7 +170,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform (452df41) at 2026-10-05T16:57:11.522Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform (452df41) at 2026-10-05T17:10:17.297Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -4990,7 +4990,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-05T16:57:14.953Z</t>
+    <t>2026-10-05T17:10:18.338Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -23937,7 +23937,7 @@
         <v>1298</v>
       </c>
       <c r="E2" s="2">
-        <v>507</v>
+        <v>552</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -24055,7 +24055,7 @@
         <v>1298</v>
       </c>
       <c r="E8" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -24073,7 +24073,7 @@
         <v>1298</v>
       </c>
       <c r="E9" s="2">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -24091,7 +24091,7 @@
         <v>1298</v>
       </c>
       <c r="E10" s="2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -24109,7 +24109,7 @@
         <v>1298</v>
       </c>
       <c r="E11" s="2">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -24127,7 +24127,7 @@
         <v>1298</v>
       </c>
       <c r="E12" s="2">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -24145,7 +24145,7 @@
         <v>1298</v>
       </c>
       <c r="E13" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -24223,7 +24223,7 @@
         <v>1298</v>
       </c>
       <c r="E17" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -24241,7 +24241,7 @@
         <v>1298</v>
       </c>
       <c r="E18" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -24299,7 +24299,7 @@
         <v>1298</v>
       </c>
       <c r="E21" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -24337,7 +24337,7 @@
         <v>1298</v>
       </c>
       <c r="E23" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -24355,7 +24355,7 @@
         <v>1298</v>
       </c>
       <c r="E24" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -24391,7 +24391,7 @@
         <v>1298</v>
       </c>
       <c r="E26" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -24409,7 +24409,7 @@
         <v>1298</v>
       </c>
       <c r="E27" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -24445,7 +24445,7 @@
         <v>1298</v>
       </c>
       <c r="E29" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -24463,7 +24463,7 @@
         <v>1298</v>
       </c>
       <c r="E30" s="2">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -24481,7 +24481,7 @@
         <v>1298</v>
       </c>
       <c r="E31" s="2">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -24519,7 +24519,7 @@
         <v>1298</v>
       </c>
       <c r="E33" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -24537,7 +24537,7 @@
         <v>1298</v>
       </c>
       <c r="E34" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -24595,7 +24595,7 @@
         <v>1298</v>
       </c>
       <c r="E37" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -24633,7 +24633,7 @@
         <v>1298</v>
       </c>
       <c r="E39" s="2">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -24651,7 +24651,7 @@
         <v>1298</v>
       </c>
       <c r="E40" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -24749,7 +24749,7 @@
         <v>1298</v>
       </c>
       <c r="E45" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -24767,7 +24767,7 @@
         <v>1298</v>
       </c>
       <c r="E46" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -24785,7 +24785,7 @@
         <v>1298</v>
       </c>
       <c r="E47" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -24823,7 +24823,7 @@
         <v>1298</v>
       </c>
       <c r="E49" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -24841,7 +24841,7 @@
         <v>1298</v>
       </c>
       <c r="E50" s="2">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -24859,7 +24859,7 @@
         <v>1298</v>
       </c>
       <c r="E51" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -24977,7 +24977,7 @@
         <v>1298</v>
       </c>
       <c r="E57" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -24995,7 +24995,7 @@
         <v>1298</v>
       </c>
       <c r="E58" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -25033,7 +25033,7 @@
         <v>1298</v>
       </c>
       <c r="E60" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -25131,7 +25131,7 @@
         <v>1298</v>
       </c>
       <c r="E65" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -25149,7 +25149,7 @@
         <v>1298</v>
       </c>
       <c r="E66" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -25225,7 +25225,7 @@
         <v>1298</v>
       </c>
       <c r="E70" s="2">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -25243,7 +25243,7 @@
         <v>1298</v>
       </c>
       <c r="E71" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -25261,7 +25261,7 @@
         <v>1298</v>
       </c>
       <c r="E72" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -25299,7 +25299,7 @@
         <v>1298</v>
       </c>
       <c r="E74" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -25317,7 +25317,7 @@
         <v>1298</v>
       </c>
       <c r="E75" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -25335,7 +25335,7 @@
         <v>1298</v>
       </c>
       <c r="E76" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -25353,7 +25353,7 @@
         <v>1298</v>
       </c>
       <c r="E77" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -25411,7 +25411,7 @@
         <v>1298</v>
       </c>
       <c r="E80" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -25429,7 +25429,7 @@
         <v>1298</v>
       </c>
       <c r="E81" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -25447,7 +25447,7 @@
         <v>1298</v>
       </c>
       <c r="E82" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -25525,7 +25525,7 @@
         <v>1298</v>
       </c>
       <c r="E86" s="2">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -25543,7 +25543,7 @@
         <v>1298</v>
       </c>
       <c r="E87" s="2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -25561,7 +25561,7 @@
         <v>1298</v>
       </c>
       <c r="E88" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -25579,7 +25579,7 @@
         <v>1298</v>
       </c>
       <c r="E89" s="2">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -25597,7 +25597,7 @@
         <v>1298</v>
       </c>
       <c r="E90" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -25635,7 +25635,7 @@
         <v>1298</v>
       </c>
       <c r="E92" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -25673,7 +25673,7 @@
         <v>1298</v>
       </c>
       <c r="E94" s="2">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -25751,7 +25751,7 @@
         <v>1298</v>
       </c>
       <c r="E98" s="2">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -25907,7 +25907,7 @@
         <v>1298</v>
       </c>
       <c r="E106" s="2">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -26045,7 +26045,7 @@
         <v>1298</v>
       </c>
       <c r="E113" s="2">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -26123,7 +26123,7 @@
         <v>1298</v>
       </c>
       <c r="E117" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -26141,7 +26141,7 @@
         <v>1298</v>
       </c>
       <c r="E118" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -26159,7 +26159,7 @@
         <v>1301</v>
       </c>
       <c r="E119" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -26177,7 +26177,7 @@
         <v>1298</v>
       </c>
       <c r="E120" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -26195,7 +26195,7 @@
         <v>1298</v>
       </c>
       <c r="E121" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -26213,7 +26213,7 @@
         <v>1301</v>
       </c>
       <c r="E122" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -26249,7 +26249,7 @@
         <v>1298</v>
       </c>
       <c r="E124" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -26267,7 +26267,7 @@
         <v>1298</v>
       </c>
       <c r="E125" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -26303,7 +26303,7 @@
         <v>1298</v>
       </c>
       <c r="E127" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -26321,7 +26321,7 @@
         <v>1298</v>
       </c>
       <c r="E128" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -26339,7 +26339,7 @@
         <v>1298</v>
       </c>
       <c r="E129" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -26357,7 +26357,7 @@
         <v>1298</v>
       </c>
       <c r="E130" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -26375,7 +26375,7 @@
         <v>1301</v>
       </c>
       <c r="E131" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -26393,7 +26393,7 @@
         <v>1298</v>
       </c>
       <c r="E132" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -26411,7 +26411,7 @@
         <v>1298</v>
       </c>
       <c r="E133" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F133" s="2"/>
     </row>
